--- a/sampleprojects/CorporateTax/excel/states/NH_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/NH_corp.xlsx
@@ -193,13 +193,13 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
+    <t>nh_apportionment</t>
   </si>
   <si>
     <t>(3 attributes)</t>
   </si>
   <si>
-    <t>nh_economic_nexus_threshold</t>
+    <t>economic_nexus_threshold</t>
   </si>
   <si>
     <t>double</t>
@@ -214,7 +214,7 @@
     <t>NH economic nexus gross receipts threshold: $109,000 (2025)</t>
   </si>
   <si>
-    <t>nh_state_tax_rate</t>
+    <t>state_tax_rate</t>
   </si>
   <si>
     <t>0.075</t>
@@ -223,7 +223,7 @@
     <t>NH Business Profits Tax rate: 7.5% flat rate (RSA 77-A:2)</t>
   </si>
   <si>
-    <t>nh_transaction_threshold</t>
+    <t>transaction_threshold</t>
   </si>
   <si>
     <t>integer</t>
@@ -235,13 +235,13 @@
     <t>NH has no transaction count threshold - only gross receipts</t>
   </si>
   <si>
-    <t>result</t>
+    <t>nh_result</t>
   </si>
   <si>
     <t>(1 attributes)</t>
   </si>
   <si>
-    <t>nh_irc_conformity_date</t>
+    <t>irc_conformity_date</t>
   </si>
   <si>
     <t>string</t>
